--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -1160,6 +1160,10 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:$this.resolve()}
+</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -6933,7 +6937,7 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -6961,7 +6965,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -6969,13 +6973,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>353</v>
@@ -6997,7 +7001,7 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>355</v>
@@ -7076,7 +7080,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7084,13 +7088,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>353</v>
@@ -7112,7 +7116,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>355</v>
@@ -7191,7 +7195,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7199,13 +7203,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>353</v>
@@ -7227,7 +7231,7 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>355</v>
@@ -7306,7 +7310,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7314,13 +7318,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>353</v>
@@ -7342,7 +7346,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>355</v>
@@ -7421,7 +7425,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7429,13 +7433,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>353</v>
@@ -7457,7 +7461,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>355</v>
@@ -7536,7 +7540,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7544,13 +7548,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>353</v>
@@ -7572,7 +7576,7 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>355</v>
@@ -7651,7 +7655,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7659,13 +7663,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>353</v>
@@ -7687,7 +7691,7 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>355</v>
@@ -7766,7 +7770,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7774,13 +7778,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>353</v>
@@ -7802,7 +7806,7 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>355</v>
@@ -7881,7 +7885,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -7889,13 +7893,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>353</v>
@@ -7917,7 +7921,7 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>355</v>
@@ -7996,7 +8000,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8004,13 +8008,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>353</v>
@@ -8032,7 +8036,7 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>355</v>
@@ -8111,7 +8115,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8119,13 +8123,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>353</v>
@@ -8147,7 +8151,7 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>355</v>
@@ -8226,7 +8230,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8234,13 +8238,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>353</v>
@@ -8262,7 +8266,7 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>355</v>
@@ -8341,7 +8345,7 @@
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8349,10 +8353,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8375,16 +8379,16 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8434,7 +8438,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8460,14 +8464,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8486,17 +8490,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -8545,7 +8549,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8563,7 +8567,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8571,10 +8575,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8680,10 +8684,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8791,14 +8795,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8820,10 +8824,10 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>111</v>
@@ -8878,7 +8882,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8904,10 +8908,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8933,16 +8937,16 @@
         <v>102</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -8991,7 +8995,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9017,10 +9021,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9043,13 +9047,13 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9100,7 +9104,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9126,14 +9130,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9155,14 +9159,14 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9211,7 +9215,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9229,7 +9233,7 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
@@ -9237,10 +9241,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9266,10 +9270,10 @@
         <v>223</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9299,10 +9303,10 @@
         <v>153</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9320,7 +9324,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9338,7 +9342,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9346,10 +9350,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9455,10 +9459,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9566,10 +9570,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9677,13 +9681,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="B71" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="C71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
@@ -9727,7 +9731,7 @@
         <v>79</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>79</v>
@@ -9792,10 +9796,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>250</v>
@@ -9842,7 +9846,7 @@
         <v>79</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>79</v>
@@ -9861,7 +9865,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>79</v>
@@ -9905,10 +9909,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10018,10 +10022,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10044,19 +10048,19 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10105,7 +10109,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10123,7 +10127,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -1437,7 +1437,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
